--- a/Financial Analysis/SAF.xlsx
+++ b/Financial Analysis/SAF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CA1591-7A65-42F2-80E2-81B2BC64B811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F910198-CC65-43E4-A55A-5FEF2AE40AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0E829F47-3703-4ED3-886F-B32F8228A069}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0E829F47-3703-4ED3-886F-B32F8228A069}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
   <si>
     <t>SAF</t>
   </si>
@@ -202,17 +202,27 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +247,15 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -285,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -304,6 +323,8 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -750,14 +771,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>284.89999999999998</v>
+        <v>303.10000000000002</v>
       </c>
       <c r="E3" s="5">
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="5">
         <v>46066</v>
@@ -781,7 +802,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>119059.70999999998</v>
+        <v>126665.49</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -823,7 +844,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>115605.70999999998</v>
+        <v>123211.49</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0400A084-67EA-4632-BC66-83DBCE4959D5}">
-  <dimension ref="B2:EH40"/>
+  <dimension ref="B2:EH42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1109,7 +1130,7 @@
         <v>38916.057290572804</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" ref="V5:AB5" si="2">V5*1.02</f>
+        <f t="shared" ref="W5:AB5" si="2">V5*1.02</f>
         <v>39694.378436384264</v>
       </c>
       <c r="X5" s="9">
@@ -3427,47 +3448,47 @@
         <v>416.1</v>
       </c>
       <c r="R28" s="6">
-        <f>417.9</f>
+        <f t="shared" ref="R28:AB28" si="42">417.9</f>
         <v>417.9</v>
       </c>
       <c r="S28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="T28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="U28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="V28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="W28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="X28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="Y28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="Z28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="AA28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
       <c r="AB28" s="6">
-        <f>417.9</f>
+        <f t="shared" si="42"/>
         <v>417.9</v>
       </c>
     </row>
@@ -3492,79 +3513,79 @@
         <v>-5.044460466234078</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" ref="I29:J29" si="42">I27/I28</f>
+        <f t="shared" ref="I29:J29" si="43">I27/I28</f>
         <v>12.072266092366595</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>4.0154755683177807</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" ref="L29:S29" si="43">L27/L28</f>
+        <f t="shared" ref="L29:S29" si="44">L27/L28</f>
         <v>6.2750176595243703</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.9770438041695948</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.7806935332708529</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2.7743758831841734</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.243178554332216</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-1.6029800528719058</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>16.087741660684372</v>
       </c>
       <c r="S29" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.864849799952145</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" ref="T29:AB29" si="44">T27/T28</f>
+        <f t="shared" ref="T29:AB29" si="45">T27/T28</f>
         <v>12.596276305896149</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>13.117684817647909</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>13.528156202481913</v>
       </c>
       <c r="W29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>13.815337752365116</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.108783865081651</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.408641543892285</v>
       </c>
       <c r="Z29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.715061737336518</v>
       </c>
       <c r="AA29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>15.028199466483771</v>
       </c>
       <c r="AB29" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>15.348213957094357</v>
       </c>
     </row>
@@ -3583,28 +3604,28 @@
         <v>0.15014667284236527</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" ref="I31:J31" si="45">I5/G5-1</f>
+        <f t="shared" ref="I31:J31" si="46">I5/G5-1</f>
         <v>0.1373066767257638</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.11814752667964301</v>
       </c>
       <c r="L31" s="10"/>
       <c r="M31" s="10">
-        <f t="shared" ref="M31:P31" si="46">M5/L5-1</f>
+        <f t="shared" ref="M31:P31" si="47">M5/L5-1</f>
         <v>-0.32770581866303083</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-6.7700566656725303E-2</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.24600127959053109</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.23876765083440299</v>
       </c>
       <c r="Q31" s="10">
@@ -3616,43 +3637,43 @@
         <v>0.1271677203949706</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" ref="S31:AB31" si="47">S5/R5-1</f>
+        <f t="shared" ref="S31:AB31" si="48">S5/R5-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3661,15 +3682,15 @@
         <v>46</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" ref="E32:G32" si="48">E11/E5</f>
+        <f t="shared" ref="E32:G32" si="49">E11/E5</f>
         <v>0.16283233372124251</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.19044310637640882</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.17864956620143344</v>
       </c>
       <c r="H32" s="10">
@@ -3677,31 +3698,31 @@
         <v>0.20229545607087723</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" ref="I32:J32" si="49">I11/I5</f>
+        <f t="shared" ref="I32:J32" si="50">I11/I5</f>
         <v>0.21107794361525706</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.2</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" ref="L32:P32" si="50">L11/L5</f>
+        <f t="shared" ref="L32:P32" si="51">L11/L5</f>
         <v>0.18454505353490797</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.14440799284223083</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.16154830454254637</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.16323491655969191</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.1776580310880829</v>
       </c>
       <c r="Q32" s="10">
@@ -3713,43 +3734,43 @@
         <v>0.20526244805302024</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" ref="S32:AB32" si="51">S11/S5</f>
+        <f t="shared" ref="S32:AB32" si="52">S11/S5</f>
         <v>0.2</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="U32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.2</v>
       </c>
       <c r="AE32" s="1" t="s">
@@ -3764,15 +3785,15 @@
         <v>47</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" ref="E33:G33" si="52">E19/E5</f>
+        <f t="shared" ref="E33:G33" si="53">E19/E5</f>
         <v>0.11995345089965088</v>
       </c>
       <c r="F33" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.11255210745715609</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.14711429649188984</v>
       </c>
       <c r="H33" s="10">
@@ -3780,31 +3801,31 @@
         <v>0.15047989797973019</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" ref="I33:J33" si="53">I19/I5</f>
+        <f t="shared" ref="I33:J33" si="54">I19/I5</f>
         <v>0.1612603648424544</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.13537355756071093</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" ref="L33:P33" si="54">L19/L5</f>
+        <f t="shared" ref="L33:P33" si="55">L19/L5</f>
         <v>0.15370734250310783</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>7.2770653146436021E-2</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>8.9571337172104928E-2</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.10053915275994865</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.11597927461139897</v>
       </c>
       <c r="Q33" s="10">
@@ -3816,43 +3837,43 @@
         <v>0.14767078377073622</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" ref="S33:AB33" si="55">S19/S5</f>
+        <f t="shared" ref="S33:AB33" si="56">S19/S5</f>
         <v>0.19346149582652508</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19390286599359391</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19421297338496171</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19446217773873753</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19465732957481574</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19485471108292163</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19505442225427033</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.1952565656836163</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19546124664913578</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.19566857319462619</v>
       </c>
       <c r="AE33" s="1" t="s">
@@ -3867,15 +3888,15 @@
         <v>30</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" ref="E34:G34" si="56">E25/E24</f>
+        <f t="shared" ref="E34:G34" si="57">E25/E24</f>
         <v>0.22665716322166785</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.27378467044437815</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.22703549060542796</v>
       </c>
       <c r="H34" s="10">
@@ -3883,31 +3904,31 @@
         <v>0.25909909909909912</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" ref="I34:J34" si="57">I25/I24</f>
+        <f t="shared" ref="I34:J34" si="58">I25/I24</f>
         <v>0.28712871287128711</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.26</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" ref="L34:P34" si="58">L25/L24</f>
+        <f t="shared" ref="L34:P34" si="59">L25/L24</f>
         <v>0.27029914529914528</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.27535037098103876</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.34448160535117056</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.31433408577878102</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.25988225399495374</v>
       </c>
       <c r="Q34" s="10">
@@ -3919,43 +3940,43 @@
         <v>0.28046448296095638</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" ref="S34:AB34" si="59">S25/S24</f>
+        <f t="shared" ref="S34:AB34" si="60">S25/S24</f>
         <v>0.25</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="AA34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
       <c r="AE34" s="1" t="s">
@@ -3971,15 +3992,15 @@
         <v>48</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" ref="E35:G35" si="60">E27/E5</f>
+        <f t="shared" ref="E35:G35" si="61">E27/E5</f>
         <v>9.3366753200250646E-2</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.18534815501003551</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.10803470388532629</v>
       </c>
       <c r="H35" s="10">
@@ -3987,31 +4008,31 @@
         <v>-0.14088193838512653</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" ref="I35:J35" si="61">I27/I5</f>
+        <f t="shared" ref="I35:J35" si="62">I27/I5</f>
         <v>0.33466003316749587</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.10072867734980144</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" ref="L35:P35" si="62">L27/L5</f>
+        <f t="shared" ref="L35:P35" si="63">L27/L5</f>
         <v>0.10686931066287043</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5.034297643900984E-2</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>4.8624440179142678E-2</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>6.0487804878048779E-2</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.14275647668393782</v>
       </c>
       <c r="Q35" s="10">
@@ -4023,43 +4044,43 @@
         <v>0.21185504255965468</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" ref="S35:AB35" si="63">S27/S5</f>
+        <f t="shared" ref="S35:AB35" si="64">S27/S5</f>
         <v>0.14467124239967821</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14489596100523328</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14509015796987496</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14527207714813134</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14544703492375127</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14562393895735617</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14580286536603704</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14598389219809119</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14616709949163656</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.14635256933492069</v>
       </c>
       <c r="AE35" s="1" t="s">
@@ -4094,16 +4115,22 @@
       </c>
       <c r="AF38" s="4">
         <f>Main!D3</f>
-        <v>284.89999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.3">
+        <v>303.10000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" s="12">
+        <v>55012</v>
+      </c>
       <c r="AE39" s="3" t="s">
         <v>56</v>
       </c>
       <c r="AF39" s="11">
         <f>AF37/AF38-1</f>
-        <v>-0.28700962633957428</v>
+        <v>-0.32982198133996943</v>
       </c>
     </row>
     <row r="40" spans="2:32" x14ac:dyDescent="0.3">
@@ -4112,6 +4139,24 @@
       </c>
       <c r="AF40" s="7" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I41" s="13">
+        <f>Main!D9/Model!I39</f>
+        <v>2.2397202428561043</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I42" s="10">
+        <f>I39/Main!D9-1</f>
+        <v>-0.55351566643662864</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SAF.xlsx
+++ b/Financial Analysis/SAF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F910198-CC65-43E4-A55A-5FEF2AE40AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1719E6D4-31A3-4FFF-9126-7F4E70259DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0E829F47-3703-4ED3-886F-B32F8228A069}"/>
   </bookViews>
@@ -202,9 +202,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
     <t>L+S/E</t>
   </si>
   <si>
@@ -212,6 +209,9 @@
   </si>
   <si>
     <t>B/EV</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -778,7 +778,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45934</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="5">
         <v>46066</v>
@@ -3880,7 +3880,7 @@
         <v>50</v>
       </c>
       <c r="AF33" s="10">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="34" spans="2:32" x14ac:dyDescent="0.3">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AF34" s="6">
         <f>NPV(AF33,R27:EH27)</f>
-        <v>81434.42712080192</v>
+        <v>93796.75475402041</v>
       </c>
     </row>
     <row r="35" spans="2:32" x14ac:dyDescent="0.3">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AF36" s="6">
         <f>AF34+AF35</f>
-        <v>84888.42712080192</v>
+        <v>97250.75475402041</v>
       </c>
     </row>
     <row r="37" spans="2:32" x14ac:dyDescent="0.3">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AF37" s="4">
         <f>AF36/AB28</f>
-        <v>203.13095745585528</v>
+        <v>232.71298098593064</v>
       </c>
     </row>
     <row r="38" spans="2:32" x14ac:dyDescent="0.3">
@@ -4120,7 +4120,7 @@
     </row>
     <row r="39" spans="2:32" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I39" s="12">
         <v>55012</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AF39" s="11">
         <f>AF37/AF38-1</f>
-        <v>-0.32982198133996943</v>
+        <v>-0.23222375128363371</v>
       </c>
     </row>
     <row r="40" spans="2:32" x14ac:dyDescent="0.3">
@@ -4138,12 +4138,12 @@
         <v>57</v>
       </c>
       <c r="AF40" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I41" s="13">
         <f>Main!D9/Model!I39</f>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="42" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I42" s="10">
         <f>I39/Main!D9-1</f>
